--- a/excel-files/LAS PINAS/CAA ELEMENTARY SCHOOL MAIN.xlsx
+++ b/excel-files/LAS PINAS/CAA ELEMENTARY SCHOOL MAIN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{683FA1F1-517F-46BD-8668-0F756C660D37}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{037CDAEF-ABDA-4D44-8015-65541AAB0409}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -631,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -759,6 +759,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5417,15 +5420,12 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{1940F638-443F-4471-B54B-87F0A4281369}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10042,7 +10042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10056,7 +10056,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10691,7 +10691,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11326,7 +11326,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11961,7 +11961,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>25</v>
       </c>
@@ -11989,7 +11989,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="5"/>
-      <c r="L103" s="1"/>
+      <c r="L103" s="32"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5">
         <f t="shared" si="16"/>
@@ -12058,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="K104" s="5"/>
-      <c r="L104" s="1"/>
+      <c r="L104" s="32"/>
       <c r="M104" s="5"/>
       <c r="N104" s="5">
         <f t="shared" si="16"/>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="5"/>
-      <c r="L105" s="1"/>
+      <c r="L105" s="32"/>
       <c r="M105" s="5"/>
       <c r="N105" s="5">
         <f t="shared" si="16"/>
@@ -12196,7 +12196,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="5"/>
-      <c r="L106" s="1"/>
+      <c r="L106" s="32"/>
       <c r="M106" s="5"/>
       <c r="N106" s="5">
         <f t="shared" si="16"/>
@@ -12265,7 +12265,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="5"/>
-      <c r="L107" s="1"/>
+      <c r="L107" s="32"/>
       <c r="M107" s="5"/>
       <c r="N107" s="5">
         <f t="shared" si="16"/>
@@ -12334,7 +12334,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="5"/>
-      <c r="L108" s="1"/>
+      <c r="L108" s="32"/>
       <c r="M108" s="5"/>
       <c r="N108" s="5">
         <f t="shared" si="16"/>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="5"/>
-      <c r="L109" s="1"/>
+      <c r="L109" s="32"/>
       <c r="M109" s="5"/>
       <c r="N109" s="5">
         <f t="shared" si="16"/>
@@ -12472,7 +12472,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="5"/>
-      <c r="L110" s="1"/>
+      <c r="L110" s="32"/>
       <c r="M110" s="5"/>
       <c r="N110" s="5">
         <f t="shared" si="16"/>
@@ -12513,7 +12513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12524,7 +12524,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12545,7 +12545,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="5"/>
-      <c r="L112" s="1"/>
+      <c r="L112" s="32"/>
       <c r="M112" s="5"/>
       <c r="N112" s="5">
         <f t="shared" si="16"/>
@@ -12607,7 +12607,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="5"/>
-      <c r="L113" s="1"/>
+      <c r="L113" s="32"/>
       <c r="M113" s="5"/>
       <c r="N113" s="5">
         <f t="shared" si="16"/>
@@ -12669,7 +12669,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="5"/>
-      <c r="L114" s="1"/>
+      <c r="L114" s="32"/>
       <c r="M114" s="5"/>
       <c r="N114" s="5">
         <f t="shared" si="16"/>
@@ -12731,7 +12731,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="5"/>
-      <c r="L115" s="1"/>
+      <c r="L115" s="32"/>
       <c r="M115" s="5"/>
       <c r="N115" s="5">
         <f t="shared" si="16"/>
@@ -12793,7 +12793,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="5"/>
-      <c r="L116" s="1"/>
+      <c r="L116" s="32"/>
       <c r="M116" s="5"/>
       <c r="N116" s="5">
         <f t="shared" si="16"/>
@@ -12855,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="5"/>
-      <c r="L117" s="1"/>
+      <c r="L117" s="32"/>
       <c r="M117" s="5"/>
       <c r="N117" s="5">
         <f t="shared" si="16"/>
@@ -12917,7 +12917,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="5"/>
-      <c r="L118" s="1"/>
+      <c r="L118" s="32"/>
       <c r="M118" s="5"/>
       <c r="N118" s="5">
         <f t="shared" si="16"/>
@@ -12979,7 +12979,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="5"/>
-      <c r="L119" s="1"/>
+      <c r="L119" s="32"/>
       <c r="M119" s="5"/>
       <c r="N119" s="5">
         <f t="shared" si="16"/>
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="5"/>
-      <c r="L120" s="1"/>
+      <c r="L120" s="32"/>
       <c r="M120" s="5"/>
       <c r="N120" s="5">
         <f t="shared" si="16"/>
@@ -13103,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5"/>
-      <c r="L121" s="1"/>
+      <c r="L121" s="32"/>
       <c r="M121" s="5"/>
       <c r="N121" s="5">
         <f t="shared" si="16"/>
@@ -13165,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="5"/>
-      <c r="L122" s="1"/>
+      <c r="L122" s="32"/>
       <c r="M122" s="5"/>
       <c r="N122" s="5">
         <f t="shared" si="16"/>
@@ -13227,7 +13227,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="5"/>
-      <c r="L123" s="1"/>
+      <c r="L123" s="32"/>
       <c r="M123" s="5"/>
       <c r="N123" s="5">
         <f t="shared" si="16"/>
@@ -13289,7 +13289,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="5"/>
-      <c r="L124" s="1"/>
+      <c r="L124" s="32"/>
       <c r="M124" s="5"/>
       <c r="N124" s="5">
         <f t="shared" si="16"/>
@@ -13351,7 +13351,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="5"/>
-      <c r="L125" s="1"/>
+      <c r="L125" s="32"/>
       <c r="M125" s="5"/>
       <c r="N125" s="5">
         <f t="shared" si="16"/>
@@ -13413,7 +13413,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="5"/>
-      <c r="L126" s="1"/>
+      <c r="L126" s="32"/>
       <c r="M126" s="5"/>
       <c r="N126" s="5">
         <f t="shared" si="16"/>
@@ -13475,7 +13475,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="46"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13502,7 +13502,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13696,7 +13696,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C33:C41 C43:C51 C53:C61" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 Q14:R21 W14:X21 Q23:R31 W23:X31 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 H53:I61 Q53:R61 W53:X61 H63:I71 Q63:R71 W63:X71 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 H93:I101 Q93:R101 W93:X101 H103:I110 Q103:R110 W103:X110 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 H103:I110 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 K112:K127 Q112:Q126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 L112:L126 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 R112:R127 T5:X12 W63:X71 W103:X110 W112:X127 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W73:X81 W83:X91 W93:X101" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13706,17 +13706,20 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 X103:X110 R83:R91 R93:R101 R14:R21 R5:R12 L103:L110 R103:R110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127" xr:uid="{2A9DF2F1-ED9E-4939-A86E-4455B43B2BAB}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L126 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X53:X61 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X83:X91 X93:X101" xr:uid="{6C62FD33-976B-4C09-B0FB-65C25F35D390}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14430,8 +14433,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14983,8 +14986,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15605,8 +15608,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -16365,8 +16368,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -17125,8 +17128,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -18645,8 +18648,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -19405,8 +19408,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -20165,8 +20168,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20926,7 +20929,7 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>25</v>
       </c>
@@ -21992,7 +21995,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D103:F113 D115:F122" name="LAS"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D103:F113 D115:F122 H3:L10 H67:L77 H115:L122 H103:L113 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H79:L89 H91:L101 P2:R10 N67:R77 N115:R122 N103:R113 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N79:R89 N91:R101 V2:X10 T67:X77 T115:X122 T103:X113 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T79:X89 T91:X101" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22002,14 +22005,17 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 R115:R122 X115:X122 L115:L122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122" xr:uid="{10878E16-6949-4423-9CCA-CF9DB649C966}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L103:L113 L115:L122 L55:L65 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L91:L101 R103:R113 R115:R122 R55:R65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R91:R101 X103:X113 X55:X65 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X91:X101" xr:uid="{D258184D-9590-4DC2-8734-EEF17DCE963B}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
